--- a/data/incident_register.xlsx
+++ b/data/incident_register.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>45457</v>
+        <v>45487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="J2" s="1" t="n">
-        <v>45459</v>
+        <v>45489</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>45446</v>
+        <v>45476</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="J3" s="1" t="n">
-        <v>45448</v>
+        <v>45478</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>45493</v>
+        <v>45523</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>45460</v>
+        <v>45490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="J4" s="1" t="n">
-        <v>45460</v>
+        <v>45490</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>45517</v>
+        <v>45547</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>45446</v>
+        <v>45476</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="J5" s="1" t="n">
-        <v>45447</v>
+        <v>45477</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>45458</v>
+        <v>45488</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>45460</v>
+        <v>45490</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>45457</v>
+        <v>45487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>45459</v>
+        <v>45489</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>45464</v>
+        <v>45495</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>45466</v>
+        <v>45497</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>45460</v>
+        <v>45491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>45461</v>
+        <v>45492</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>45476</v>
+        <v>45507</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>45469</v>
+        <v>45500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>45470</v>
+        <v>45501</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>45511</v>
+        <v>45542</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>45462</v>
+        <v>45492</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>45462</v>
+        <v>45492</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>45522</v>
+        <v>45552</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>45468</v>
+        <v>45499</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>45468</v>
+        <v>45499</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>45463</v>
+        <v>45494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>45465</v>
+        <v>45496</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>45510</v>
+        <v>45541</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>45449</v>
+        <v>45479</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>45451</v>
+        <v>45481</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>45498</v>
+        <v>45528</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>45477</v>
+        <v>45508</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>45478</v>
+        <v>45509</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>45498</v>
+        <v>45529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>45499</v>
+        <v>45530</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>45516</v>
+        <v>45547</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>45496</v>
+        <v>45527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>45496</v>
+        <v>45527</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>45500</v>
+        <v>45531</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="J18" s="1" t="n">
-        <v>45501</v>
+        <v>45532</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>45535</v>
+        <v>45566</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>45494</v>
+        <v>45525</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>45496</v>
+        <v>45527</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>45479</v>
+        <v>45510</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="J20" s="1" t="n">
-        <v>45480</v>
+        <v>45511</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>45492</v>
+        <v>45523</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="J21" s="1" t="n">
-        <v>45492</v>
+        <v>45523</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>45482</v>
+        <v>45513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="J22" s="1" t="n">
-        <v>45483</v>
+        <v>45514</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>45517</v>
+        <v>45548</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>45514</v>
+        <v>45545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="n">
-        <v>45515</v>
+        <v>45546</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>45513</v>
+        <v>45544</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="J24" s="1" t="n">
-        <v>45515</v>
+        <v>45546</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>45512</v>
+        <v>45542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>45513</v>
+        <v>45543</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>45544</v>
+        <v>45574</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>45514</v>
+        <v>45545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="J26" s="1" t="n">
-        <v>45515</v>
+        <v>45546</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>45514</v>
+        <v>45544</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>45515</v>
+        <v>45545</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>45528</v>
+        <v>45558</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="J28" s="1" t="n">
-        <v>45528</v>
+        <v>45558</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>45558</v>
+        <v>45589</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="J29" s="1" t="n">
-        <v>45558</v>
+        <v>45589</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>45541</v>
+        <v>45572</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="J30" s="1" t="n">
-        <v>45541</v>
+        <v>45572</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>45544</v>
+        <v>45574</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="J31" s="1" t="n">
-        <v>45544</v>
+        <v>45574</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>45603</v>
+        <v>45633</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>45548</v>
+        <v>45578</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="J32" s="1" t="n">
-        <v>45548</v>
+        <v>45578</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>45563</v>
+        <v>45593</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>45553</v>
+        <v>45583</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="J33" s="1" t="n">
-        <v>45555</v>
+        <v>45585</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>45550</v>
+        <v>45581</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="J34" s="1" t="n">
-        <v>45551</v>
+        <v>45582</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>45578</v>
+        <v>45609</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>45552</v>
+        <v>45583</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="J35" s="1" t="n">
-        <v>45554</v>
+        <v>45585</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>45574</v>
+        <v>45605</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>45573</v>
+        <v>45603</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="J36" s="1" t="n">
-        <v>45575</v>
+        <v>45605</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>45629</v>
+        <v>45659</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>45577</v>
+        <v>45608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="J37" s="1" t="n">
-        <v>45579</v>
+        <v>45610</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>45592</v>
+        <v>45622</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="J38" s="1" t="n">
-        <v>45594</v>
+        <v>45624</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>45584</v>
+        <v>45614</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="J39" s="1" t="n">
-        <v>45584</v>
+        <v>45614</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>45583</v>
+        <v>45614</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="J40" s="1" t="n">
-        <v>45583</v>
+        <v>45614</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>45567</v>
+        <v>45598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="J41" s="1" t="n">
-        <v>45568</v>
+        <v>45599</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>45588</v>
+        <v>45619</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="J42" s="1" t="n">
-        <v>45590</v>
+        <v>45621</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>45571</v>
+        <v>45602</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="J43" s="1" t="n">
-        <v>45572</v>
+        <v>45603</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>45604</v>
+        <v>45634</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="J44" s="1" t="n">
-        <v>45606</v>
+        <v>45636</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>45616</v>
+        <v>45646</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="J45" s="1" t="n">
-        <v>45618</v>
+        <v>45648</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>45657</v>
+        <v>45687</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>45610</v>
+        <v>45641</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="J46" s="1" t="n">
-        <v>45610</v>
+        <v>45641</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>45607</v>
+        <v>45637</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="J47" s="1" t="n">
-        <v>45608</v>
+        <v>45638</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>45608</v>
+        <v>45638</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="J48" s="1" t="n">
-        <v>45610</v>
+        <v>45640</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>45668</v>
+        <v>45698</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>45606</v>
+        <v>45637</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="J49" s="1" t="n">
-        <v>45607</v>
+        <v>45638</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>45651</v>
+        <v>45682</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>45649</v>
+        <v>45680</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="J50" s="1" t="n">
-        <v>45651</v>
+        <v>45682</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="J51" s="1" t="n">
-        <v>45659</v>
+        <v>45690</v>
       </c>
       <c r="K51" s="1" t="n">
-        <v>45677</v>
+        <v>45708</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>45632</v>
+        <v>45663</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="J52" s="1" t="n">
-        <v>45632</v>
+        <v>45663</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>45641</v>
+        <v>45672</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="J53" s="1" t="n">
-        <v>45643</v>
+        <v>45674</v>
       </c>
       <c r="K53" s="1" t="n">
-        <v>45694</v>
+        <v>45725</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>45655</v>
+        <v>45686</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="J54" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>45649</v>
+        <v>45680</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="J55" s="1" t="n">
-        <v>45650</v>
+        <v>45681</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>45702</v>
+        <v>45733</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>45636</v>
+        <v>45667</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="J56" s="1" t="n">
-        <v>45636</v>
+        <v>45667</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>45640</v>
+        <v>45671</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="J57" s="1" t="n">
-        <v>45640</v>
+        <v>45671</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>45680</v>
+        <v>45709</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="J58" s="1" t="n">
-        <v>45682</v>
+        <v>45711</v>
       </c>
       <c r="K58" s="1" t="n">
-        <v>45741</v>
+        <v>45770</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>45680</v>
+        <v>45709</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="J59" s="1" t="n">
-        <v>45682</v>
+        <v>45711</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>45685</v>
+        <v>45713</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="J60" s="1" t="n">
-        <v>45685</v>
+        <v>45713</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>45679</v>
+        <v>45708</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="J61" s="1" t="n">
-        <v>45681</v>
+        <v>45710</v>
       </c>
       <c r="K61" s="1" t="n">
-        <v>45706</v>
+        <v>45735</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="J62" s="1" t="n">
-        <v>45660</v>
+        <v>45691</v>
       </c>
       <c r="K62" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="J63" s="1" t="n">
-        <v>45690</v>
+        <v>45718</v>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>45659</v>
+        <v>45690</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="J64" s="1" t="n">
-        <v>45659</v>
+        <v>45690</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>45709</v>
+        <v>45740</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>45659</v>
+        <v>45690</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="J65" s="1" t="n">
-        <v>45661</v>
+        <v>45692</v>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>45683</v>
+        <v>45711</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="J66" s="1" t="n">
-        <v>45685</v>
+        <v>45713</v>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>45680</v>
+        <v>45708</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="J67" s="1" t="n">
-        <v>45681</v>
+        <v>45709</v>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>45695</v>
+        <v>45724</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="J68" s="1" t="n">
-        <v>45697</v>
+        <v>45726</v>
       </c>
       <c r="K68" s="1" t="n">
-        <v>45730</v>
+        <v>45759</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>45693</v>
+        <v>45721</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="J69" s="1" t="n">
-        <v>45693</v>
+        <v>45721</v>
       </c>
       <c r="K69" s="1" t="n">
-        <v>45739</v>
+        <v>45767</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>45715</v>
+        <v>45746</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="J70" s="1" t="n">
-        <v>45715</v>
+        <v>45746</v>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>45706</v>
+        <v>45735</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="J71" s="1" t="n">
-        <v>45706</v>
+        <v>45735</v>
       </c>
       <c r="K71" s="1" t="n">
-        <v>45739</v>
+        <v>45768</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>45697</v>
+        <v>45726</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="J72" s="1" t="n">
-        <v>45698</v>
+        <v>45727</v>
       </c>
       <c r="K72" s="1" t="n">
-        <v>45734</v>
+        <v>45763</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>45704</v>
+        <v>45734</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="J73" s="1" t="n">
-        <v>45705</v>
+        <v>45735</v>
       </c>
       <c r="K73" s="1" t="n">
-        <v>45749</v>
+        <v>45779</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>45704</v>
+        <v>45734</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="J74" s="1" t="n">
-        <v>45705</v>
+        <v>45735</v>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>45712</v>
+        <v>45743</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="J75" s="1" t="n">
-        <v>45713</v>
+        <v>45744</v>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>45725</v>
+        <v>45756</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="J76" s="1" t="n">
-        <v>45727</v>
+        <v>45758</v>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>45729</v>
+        <v>45760</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="J77" s="1" t="n">
-        <v>45730</v>
+        <v>45761</v>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>45720</v>
+        <v>45751</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="J78" s="1" t="n">
-        <v>45720</v>
+        <v>45751</v>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>45740</v>
+        <v>45770</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="J79" s="1" t="n">
-        <v>45741</v>
+        <v>45771</v>
       </c>
       <c r="K79" s="1" t="n">
-        <v>45770</v>
+        <v>45800</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>45739</v>
+        <v>45769</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="J80" s="1" t="n">
-        <v>45739</v>
+        <v>45769</v>
       </c>
       <c r="K80" s="1" t="n">
-        <v>45796</v>
+        <v>45826</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>45737</v>
+        <v>45767</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="J81" s="1" t="n">
-        <v>45737</v>
+        <v>45767</v>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>45775</v>
+        <v>45806</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="J82" s="1" t="n">
-        <v>45775</v>
+        <v>45806</v>
       </c>
       <c r="K82" s="1" t="n">
-        <v>45802</v>
+        <v>45833</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>45762</v>
+        <v>45793</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="J83" s="1" t="n">
-        <v>45764</v>
+        <v>45795</v>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>45766</v>
+        <v>45797</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="J84" s="1" t="n">
-        <v>45766</v>
+        <v>45797</v>
       </c>
       <c r="K84" s="1" t="n">
-        <v>45814</v>
+        <v>45845</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>45763</v>
+        <v>45794</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="J85" s="1" t="n">
-        <v>45765</v>
+        <v>45796</v>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>45775</v>
+        <v>45806</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4965,10 +4965,10 @@
         </is>
       </c>
       <c r="J86" s="1" t="n">
-        <v>45776</v>
+        <v>45807</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>45806</v>
+        <v>45837</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="J87" s="1" t="n">
-        <v>45779</v>
+        <v>45810</v>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>45794</v>
+        <v>45824</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="J88" s="1" t="n">
-        <v>45795</v>
+        <v>45825</v>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>45792</v>
+        <v>45823</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="J89" s="1" t="n">
-        <v>45793</v>
+        <v>45824</v>
       </c>
       <c r="K89" s="1" t="n">
-        <v>45840</v>
+        <v>45871</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>45804</v>
+        <v>45835</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="J90" s="1" t="n">
-        <v>45806</v>
+        <v>45837</v>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>45782</v>
+        <v>45813</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="J91" s="1" t="n">
-        <v>45782</v>
+        <v>45813</v>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>45788</v>
+        <v>45819</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="J92" s="1" t="n">
-        <v>45789</v>
+        <v>45820</v>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>45820</v>
+        <v>45850</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="J93" s="1" t="n">
-        <v>45820</v>
+        <v>45850</v>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>45832</v>
+        <v>45862</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="J94" s="1" t="n">
-        <v>45833</v>
+        <v>45863</v>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>45822</v>
+        <v>45852</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="J95" s="1" t="n">
-        <v>45822</v>
+        <v>45852</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>45848</v>
+        <v>45878</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>45827</v>
+        <v>45857</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="J96" s="1" t="n">
-        <v>45829</v>
+        <v>45859</v>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>45819</v>
+        <v>45849</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="J97" s="1" t="n">
-        <v>45821</v>
+        <v>45851</v>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>45829</v>
+        <v>45860</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="J98" s="1" t="n">
-        <v>45829</v>
+        <v>45860</v>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>45833</v>
+        <v>45864</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="J99" s="1" t="n">
-        <v>45835</v>
+        <v>45866</v>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>45831</v>
+        <v>45861</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="J100" s="1" t="n">
-        <v>45832</v>
+        <v>45862</v>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>45823</v>
+        <v>45854</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="J101" s="1" t="n">
-        <v>45823</v>
+        <v>45854</v>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>45848</v>
+        <v>45879</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="J102" s="1" t="n">
-        <v>45849</v>
+        <v>45880</v>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>45859</v>
+        <v>45890</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="J103" s="1" t="n">
-        <v>45859</v>
+        <v>45890</v>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>45846</v>
+        <v>45877</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="J104" s="1" t="n">
-        <v>45848</v>
+        <v>45879</v>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>45853</v>
+        <v>45884</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="J105" s="1" t="n">
-        <v>45853</v>
+        <v>45884</v>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>45848</v>
+        <v>45879</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="J106" s="1" t="n">
-        <v>45848</v>
+        <v>45879</v>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>45854</v>
+        <v>45885</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="J107" s="1" t="n">
-        <v>45856</v>
+        <v>45887</v>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="J108" s="1" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>45840</v>
+        <v>45871</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="J109" s="1" t="n">
-        <v>45842</v>
+        <v>45873</v>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>45846</v>
+        <v>45877</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         </is>
       </c>
       <c r="J110" s="1" t="n">
-        <v>45847</v>
+        <v>45878</v>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>45885</v>
+        <v>45916</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="J111" s="1" t="n">
-        <v>45886</v>
+        <v>45917</v>
       </c>
       <c r="K111" s="1" t="n">
-        <v>45920</v>
+        <v>45951</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>45910</v>
+        <v>45941</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="J112" s="1" t="n">
-        <v>45911</v>
+        <v>45942</v>
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="J113" s="1" t="n">
-        <v>45903</v>
+        <v>45933</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="J114" s="1" t="n">
-        <v>45902</v>
+        <v>45932</v>
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>45909</v>
+        <v>45939</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="J115" s="1" t="n">
-        <v>45911</v>
+        <v>45941</v>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>45924</v>
+        <v>45954</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="J116" s="1" t="n">
-        <v>45924</v>
+        <v>45954</v>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>45953</v>
+        <v>45984</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="J117" s="1" t="n">
-        <v>45954</v>
+        <v>45985</v>
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>45953</v>
+        <v>45983</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="J118" s="1" t="n">
-        <v>45955</v>
+        <v>45985</v>
       </c>
       <c r="K118" s="1" t="n">
-        <v>45983</v>
+        <v>46013</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>45934</v>
+        <v>45965</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="J119" s="1" t="n">
-        <v>45934</v>
+        <v>45965</v>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>45948</v>
+        <v>45978</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="J120" s="1" t="n">
-        <v>45950</v>
+        <v>45980</v>
       </c>
       <c r="K120" s="1" t="n">
-        <v>45982</v>
+        <v>46012</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>45936</v>
+        <v>45966</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="J121" s="1" t="n">
-        <v>45937</v>
+        <v>45967</v>
       </c>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>45949</v>
+        <v>45979</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="J122" s="1" t="n">
-        <v>45951</v>
+        <v>45981</v>
       </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>45957</v>
+        <v>45987</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="J123" s="1" t="n">
-        <v>45957</v>
+        <v>45987</v>
       </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="B124" s="1" t="n">
-        <v>45943</v>
+        <v>45973</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="J124" s="1" t="n">
-        <v>45945</v>
+        <v>45975</v>
       </c>
       <c r="K124" s="1" t="n">
-        <v>45985</v>
+        <v>46015</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>45977</v>
+        <v>46008</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="J125" s="1" t="n">
-        <v>45979</v>
+        <v>46010</v>
       </c>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="B126" s="1" t="n">
-        <v>45969</v>
+        <v>46000</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="J126" s="1" t="n">
-        <v>45969</v>
+        <v>46000</v>
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>45989</v>
+        <v>46020</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="J127" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46006</v>
+        <v>46037</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="J128" s="1" t="n">
-        <v>46006</v>
+        <v>46037</v>
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
@@ -7179,7 +7179,7 @@
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46014</v>
+        <v>46045</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="J129" s="1" t="n">
-        <v>46015</v>
+        <v>46046</v>
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
@@ -7231,7 +7231,7 @@
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>46009</v>
+        <v>46040</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="J130" s="1" t="n">
-        <v>46011</v>
+        <v>46042</v>
       </c>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="B131" s="1" t="n">
-        <v>46003</v>
+        <v>46034</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="J131" s="1" t="n">
-        <v>46003</v>
+        <v>46034</v>
       </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>45998</v>
+        <v>46029</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         </is>
       </c>
       <c r="J132" s="1" t="n">
-        <v>45998</v>
+        <v>46029</v>
       </c>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>46000</v>
+        <v>46031</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="J133" s="1" t="n">
-        <v>46001</v>
+        <v>46032</v>
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="B134" s="1" t="n">
-        <v>45994</v>
+        <v>46025</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="J134" s="1" t="n">
-        <v>45996</v>
+        <v>46027</v>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>45995</v>
+        <v>46026</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="J135" s="1" t="n">
-        <v>45995</v>
+        <v>46026</v>
       </c>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="B136" s="1" t="n">
-        <v>46003</v>
+        <v>46034</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -7575,11 +7575,11 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Action Pending</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J136" s="1" t="n">
-        <v>46005</v>
+        <v>46036</v>
       </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>46030</v>
+        <v>46061</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="J137" s="1" t="n">
-        <v>46031</v>
+        <v>46062</v>
       </c>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="B138" s="1" t="n">
-        <v>46026</v>
+        <v>46057</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="J138" s="1" t="n">
-        <v>46028</v>
+        <v>46059</v>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
@@ -7699,7 +7699,7 @@
         </is>
       </c>
       <c r="B139" s="1" t="n">
-        <v>46052</v>
+        <v>46080</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="J139" s="1" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="B140" s="1" t="n">
-        <v>46024</v>
+        <v>46055</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="J140" s="1" t="n">
-        <v>46025</v>
+        <v>46056</v>
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="B141" s="1" t="n">
-        <v>46049</v>
+        <v>46077</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="J141" s="1" t="n">
-        <v>46050</v>
+        <v>46078</v>
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="B142" s="1" t="n">
-        <v>46025</v>
+        <v>46056</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="J142" s="1" t="n">
-        <v>46027</v>
+        <v>46058</v>
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="B143" s="1" t="n">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="J143" s="1" t="n">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="K143" s="1" t="n">
-        <v>46101</v>
+        <v>46132</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="B144" s="1" t="n">
-        <v>46061</v>
+        <v>46089</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="J144" s="1" t="n">
-        <v>46061</v>
+        <v>46089</v>
       </c>
       <c r="K144" s="1" t="n">
-        <v>46118</v>
+        <v>46146</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="B145" s="1" t="n">
-        <v>46067</v>
+        <v>46096</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="J145" s="1" t="n">
-        <v>46068</v>
+        <v>46097</v>
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
@@ -8067,7 +8067,7 @@
         </is>
       </c>
       <c r="B146" s="1" t="n">
-        <v>46077</v>
+        <v>46108</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -8103,10 +8103,10 @@
         </is>
       </c>
       <c r="J146" s="1" t="n">
-        <v>46077</v>
+        <v>46108</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>46123</v>
+        <v>46154</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="B147" s="1" t="n">
-        <v>46072</v>
+        <v>46102</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="J147" s="1" t="n">
-        <v>46073</v>
+        <v>46103</v>
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="B148" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -8205,11 +8205,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Under Investigation</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J148" s="1" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
@@ -8225,7 +8225,7 @@
         </is>
       </c>
       <c r="B149" s="1" t="n">
-        <v>46086</v>
+        <v>46117</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -8257,14 +8257,14 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Action Pending</t>
+          <t>Under Investigation</t>
         </is>
       </c>
       <c r="J149" s="1" t="n">
-        <v>46088</v>
+        <v>46119</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>46121</v>
+        <v>46152</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B150" s="1" t="n">
-        <v>46084</v>
+        <v>46115</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -8315,10 +8315,10 @@
         </is>
       </c>
       <c r="J150" s="1" t="n">
-        <v>46085</v>
+        <v>46116</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>46123</v>
+        <v>46154</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="B151" s="1" t="n">
-        <v>46100</v>
+        <v>46130</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -8365,14 +8365,14 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Under Investigation</t>
         </is>
       </c>
       <c r="J151" s="1" t="n">
-        <v>46100</v>
+        <v>46130</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>46127</v>
+        <v>46157</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="B152" s="1" t="n">
-        <v>46122</v>
+        <v>46153</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="J152" s="1" t="n">
-        <v>46123</v>
+        <v>46154</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>46155</v>
+        <v>46186</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="B153" s="1" t="n">
-        <v>46137</v>
+        <v>46168</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="J153" s="1" t="n">
-        <v>46137</v>
+        <v>46168</v>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="B154" s="1" t="n">
-        <v>46132</v>
+        <v>46163</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="J154" s="1" t="n">
-        <v>46134</v>
+        <v>46165</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>46157</v>
+        <v>46188</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="B155" s="1" t="n">
-        <v>46120</v>
+        <v>46150</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="J155" s="1" t="n">
-        <v>46122</v>
+        <v>46152</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         </is>
       </c>
       <c r="B156" s="1" t="n">
-        <v>46133</v>
+        <v>46163</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="J156" s="1" t="n">
-        <v>46135</v>
+        <v>46165</v>
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
@@ -8653,7 +8653,7 @@
         </is>
       </c>
       <c r="B157" s="1" t="n">
-        <v>46122</v>
+        <v>46152</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="J157" s="1" t="n">
-        <v>46123</v>
+        <v>46153</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>46170</v>
+        <v>46200</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="B158" s="1" t="n">
-        <v>46129</v>
+        <v>46159</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="J158" s="1" t="n">
-        <v>46130</v>
+        <v>46160</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="B159" s="1" t="n">
-        <v>46122</v>
+        <v>46153</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="J159" s="1" t="n">
-        <v>46122</v>
+        <v>46153</v>
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="B160" s="1" t="n">
-        <v>46131</v>
+        <v>46162</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="J160" s="1" t="n">
-        <v>46132</v>
+        <v>46163</v>
       </c>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="B161" s="1" t="n">
-        <v>46154</v>
+        <v>46184</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="J161" s="1" t="n">
-        <v>46155</v>
+        <v>46185</v>
       </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
@@ -8917,7 +8917,7 @@
         </is>
       </c>
       <c r="B162" s="1" t="n">
-        <v>46169</v>
+        <v>46199</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="J162" s="1" t="n">
-        <v>46169</v>
+        <v>46199</v>
       </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
@@ -8969,7 +8969,7 @@
         </is>
       </c>
       <c r="B163" s="1" t="n">
-        <v>46161</v>
+        <v>46192</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="J163" s="1" t="n">
-        <v>46161</v>
+        <v>46192</v>
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="B164" s="1" t="n">
-        <v>46148</v>
+        <v>46179</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="J164" s="1" t="n">
-        <v>46149</v>
+        <v>46180</v>
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="B165" s="1" t="n">
-        <v>46161</v>
+        <v>46191</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="J165" s="1" t="n">
-        <v>46163</v>
+        <v>46193</v>
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="B166" s="1" t="n">
-        <v>46163</v>
+        <v>46193</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="J166" s="1" t="n">
-        <v>46164</v>
+        <v>46194</v>
       </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="B167" s="1" t="n">
-        <v>46167</v>
+        <v>46197</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -9213,10 +9213,10 @@
         </is>
       </c>
       <c r="J167" s="1" t="n">
-        <v>46168</v>
+        <v>46198</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="B168" s="1" t="n">
-        <v>46146</v>
+        <v>46177</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="J168" s="1" t="n">
-        <v>46148</v>
+        <v>46179</v>
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
